--- a/Raw/redo_uws_google.xlsx
+++ b/Raw/redo_uws_google.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katia\Desktop\STAGE\M1\Travail\Indice &amp; data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katia\Desktop\STAGE\M1\Travail\Stage_M1_UWS\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7DF752-578E-4F9A-8C0F-E1CDB5F6473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB3C6BE-A2F7-402B-BC05-7D55094140A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="91">
   <si>
     <r>
       <t>Structural complexity</t>
@@ -792,6 +792,36 @@
   </si>
   <si>
     <t>November 2022</t>
+  </si>
+  <si>
+    <t>(Even)</t>
+  </si>
+  <si>
+    <t>May 2023</t>
+  </si>
+  <si>
+    <t>July 2022</t>
+  </si>
+  <si>
+    <t>April 2024</t>
+  </si>
+  <si>
+    <t>Vegetated areas but also a lot of spontaneous vegetation ! So there are the advantages of spontaneous vegetation as well, like saying unplanted species</t>
+  </si>
+  <si>
+    <t>June 2022</t>
+  </si>
+  <si>
+    <t>September 2025</t>
+  </si>
+  <si>
+    <t>(Odd)</t>
+  </si>
+  <si>
+    <t>Terre-plein semblant non piéton (marche difficile), mais avec des bancs… donc ok</t>
+  </si>
+  <si>
+    <t>May 2022</t>
   </si>
 </sst>
 </file>
@@ -950,7 +980,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -972,6 +1002,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCC00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1118,19 +1154,19 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3154,127 +3190,1028 @@
         <v>1.2777777777777777</v>
       </c>
     </row>
-    <row r="17" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="37"/>
-      <c r="Y17" s="38"/>
+    <row r="17" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="35">
+        <v>1</v>
+      </c>
+      <c r="D17" s="35">
+        <v>1</v>
+      </c>
+      <c r="E17" s="35">
+        <v>0</v>
+      </c>
+      <c r="F17" s="35">
+        <v>2</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="34">
+        <v>3</v>
+      </c>
+      <c r="J17" s="34">
+        <v>1</v>
+      </c>
+      <c r="K17" s="34">
+        <v>1</v>
+      </c>
+      <c r="L17" s="34">
+        <v>1</v>
+      </c>
+      <c r="M17" s="34">
+        <v>1</v>
+      </c>
+      <c r="N17" s="34">
+        <v>1</v>
+      </c>
+      <c r="O17" s="34">
+        <v>1</v>
+      </c>
+      <c r="P17" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="34">
+        <v>0</v>
+      </c>
+      <c r="R17" s="34">
+        <v>0</v>
+      </c>
+      <c r="S17" s="34">
+        <v>0</v>
+      </c>
+      <c r="T17" s="34">
+        <v>0</v>
+      </c>
+      <c r="U17" s="34">
+        <v>1</v>
+      </c>
+      <c r="V17" s="34">
+        <v>1</v>
+      </c>
+      <c r="W17" s="34">
+        <v>0</v>
+      </c>
+      <c r="X17" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="34">
+        <v>6</v>
+      </c>
+      <c r="AA17" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="34">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="34">
+        <v>10</v>
+      </c>
+      <c r="AD17" s="34">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="34">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="34">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="34">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
-      <c r="Y18" s="38"/>
+    <row r="18" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="35">
+        <v>5</v>
+      </c>
+      <c r="D18" s="35">
+        <v>0</v>
+      </c>
+      <c r="E18" s="35">
+        <v>0</v>
+      </c>
+      <c r="F18" s="35">
+        <v>2</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="I18" s="34">
+        <v>1</v>
+      </c>
+      <c r="J18" s="34">
+        <v>1</v>
+      </c>
+      <c r="K18" s="34">
+        <v>0</v>
+      </c>
+      <c r="L18" s="34">
+        <v>0</v>
+      </c>
+      <c r="M18" s="34">
+        <v>1</v>
+      </c>
+      <c r="N18" s="34">
+        <v>1</v>
+      </c>
+      <c r="O18" s="34">
+        <v>0</v>
+      </c>
+      <c r="P18" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="34">
+        <v>0</v>
+      </c>
+      <c r="R18" s="34">
+        <v>0</v>
+      </c>
+      <c r="S18" s="34">
+        <v>0</v>
+      </c>
+      <c r="T18" s="34">
+        <v>0</v>
+      </c>
+      <c r="U18" s="34">
+        <v>0</v>
+      </c>
+      <c r="V18" s="34">
+        <v>0</v>
+      </c>
+      <c r="W18" s="34">
+        <v>0</v>
+      </c>
+      <c r="X18" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="34">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="34">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="34">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="34">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="34">
+        <v>2.5</v>
+      </c>
+      <c r="AE18" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="34">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="34">
+        <v>1.1666666666666667</v>
+      </c>
     </row>
-    <row r="19" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
-      <c r="N19" s="38"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="38"/>
-      <c r="U19" s="38"/>
-      <c r="W19" s="38"/>
-      <c r="X19" s="38"/>
-      <c r="Y19" s="38"/>
+    <row r="19" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="35">
+        <v>7</v>
+      </c>
+      <c r="D19" s="35">
+        <v>0</v>
+      </c>
+      <c r="E19" s="35">
+        <v>0</v>
+      </c>
+      <c r="F19" s="35">
+        <v>1</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="34">
+        <v>0</v>
+      </c>
+      <c r="J19" s="34">
+        <v>1</v>
+      </c>
+      <c r="K19" s="34">
+        <v>0</v>
+      </c>
+      <c r="L19" s="34">
+        <v>0</v>
+      </c>
+      <c r="M19" s="34">
+        <v>0</v>
+      </c>
+      <c r="N19" s="38">
+        <v>0</v>
+      </c>
+      <c r="O19" s="34">
+        <v>0</v>
+      </c>
+      <c r="P19" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="38">
+        <v>1</v>
+      </c>
+      <c r="R19" s="38">
+        <v>0</v>
+      </c>
+      <c r="S19" s="34">
+        <v>0</v>
+      </c>
+      <c r="T19" s="34">
+        <v>0</v>
+      </c>
+      <c r="U19" s="38">
+        <v>0</v>
+      </c>
+      <c r="V19" s="34">
+        <v>0</v>
+      </c>
+      <c r="W19" s="38">
+        <v>0</v>
+      </c>
+      <c r="X19" s="38">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="34">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="34">
+        <v>2</v>
+      </c>
+      <c r="AC19" s="34">
+        <v>4</v>
+      </c>
+      <c r="AD19" s="34">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE19" s="34">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="34">
+        <v>2</v>
+      </c>
+      <c r="AG19" s="34">
+        <v>1.2777777777777777</v>
+      </c>
     </row>
-    <row r="20" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
-      <c r="Y20" s="38"/>
+    <row r="20" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="35">
+        <v>8</v>
+      </c>
+      <c r="D20" s="35">
+        <v>1</v>
+      </c>
+      <c r="E20" s="35">
+        <v>0</v>
+      </c>
+      <c r="F20" s="35">
+        <v>2</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="34">
+        <v>4</v>
+      </c>
+      <c r="J20" s="34">
+        <v>1</v>
+      </c>
+      <c r="K20" s="34">
+        <v>1</v>
+      </c>
+      <c r="L20" s="34">
+        <v>0</v>
+      </c>
+      <c r="M20" s="34">
+        <v>1</v>
+      </c>
+      <c r="N20" s="34">
+        <v>1</v>
+      </c>
+      <c r="O20" s="34">
+        <v>1</v>
+      </c>
+      <c r="P20" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="34">
+        <v>1</v>
+      </c>
+      <c r="R20" s="34">
+        <v>1</v>
+      </c>
+      <c r="S20" s="34">
+        <v>0</v>
+      </c>
+      <c r="T20" s="34">
+        <v>0</v>
+      </c>
+      <c r="U20" s="34">
+        <v>1</v>
+      </c>
+      <c r="V20" s="34">
+        <v>1</v>
+      </c>
+      <c r="W20" s="34">
+        <v>0</v>
+      </c>
+      <c r="X20" s="34">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="34">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="34">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="34">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="34">
+        <v>11</v>
+      </c>
+      <c r="AD20" s="34">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE20" s="34">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="34">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="34">
+        <v>3.3888888888888893</v>
+      </c>
+      <c r="AH20" s="34" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="21" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
-      <c r="Y21" s="38"/>
+    <row r="21" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="35">
+        <v>9</v>
+      </c>
+      <c r="D21" s="35">
+        <v>0</v>
+      </c>
+      <c r="E21" s="35">
+        <v>0</v>
+      </c>
+      <c r="F21" s="35">
+        <v>2</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="34">
+        <v>1</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1</v>
+      </c>
+      <c r="K21" s="34">
+        <v>0</v>
+      </c>
+      <c r="L21" s="34">
+        <v>1</v>
+      </c>
+      <c r="M21" s="34">
+        <v>1</v>
+      </c>
+      <c r="N21" s="34">
+        <v>1</v>
+      </c>
+      <c r="O21" s="34">
+        <v>0</v>
+      </c>
+      <c r="P21" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="34">
+        <v>0</v>
+      </c>
+      <c r="R21" s="34">
+        <v>0</v>
+      </c>
+      <c r="S21" s="34">
+        <v>0</v>
+      </c>
+      <c r="T21" s="34">
+        <v>0</v>
+      </c>
+      <c r="U21" s="34">
+        <v>0</v>
+      </c>
+      <c r="V21" s="34">
+        <v>1</v>
+      </c>
+      <c r="W21" s="34">
+        <v>0</v>
+      </c>
+      <c r="X21" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="34">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="34">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="34">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="34">
+        <v>6</v>
+      </c>
+      <c r="AD21" s="34">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AE21" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="34">
+        <v>2</v>
+      </c>
+      <c r="AG21" s="34">
+        <v>1.7777777777777777</v>
+      </c>
     </row>
-    <row r="22" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="37"/>
-      <c r="Y22" s="38"/>
+    <row r="22" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="35">
+        <v>11</v>
+      </c>
+      <c r="D22" s="35">
+        <v>0</v>
+      </c>
+      <c r="E22" s="35">
+        <v>1</v>
+      </c>
+      <c r="F22" s="35">
+        <v>1</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" s="34">
+        <v>1</v>
+      </c>
+      <c r="J22" s="34">
+        <v>1</v>
+      </c>
+      <c r="K22" s="34">
+        <v>0</v>
+      </c>
+      <c r="L22" s="34">
+        <v>0</v>
+      </c>
+      <c r="M22" s="34">
+        <v>0</v>
+      </c>
+      <c r="N22" s="34">
+        <v>0</v>
+      </c>
+      <c r="O22" s="34">
+        <v>0</v>
+      </c>
+      <c r="P22" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="34">
+        <v>1</v>
+      </c>
+      <c r="R22" s="34">
+        <v>0</v>
+      </c>
+      <c r="S22" s="34">
+        <v>0</v>
+      </c>
+      <c r="T22" s="34">
+        <v>0</v>
+      </c>
+      <c r="U22" s="34">
+        <v>0</v>
+      </c>
+      <c r="V22" s="34">
+        <v>0</v>
+      </c>
+      <c r="W22" s="34">
+        <v>0</v>
+      </c>
+      <c r="X22" s="34">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="34">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="34">
+        <v>2</v>
+      </c>
+      <c r="AC22" s="34">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="34">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE22" s="34">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="34">
+        <v>2</v>
+      </c>
+      <c r="AG22" s="34">
+        <v>1.2777777777777777</v>
+      </c>
     </row>
-    <row r="23" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
-      <c r="Y23" s="38"/>
+    <row r="23" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="35">
+        <v>19</v>
+      </c>
+      <c r="D23" s="35">
+        <v>0</v>
+      </c>
+      <c r="E23" s="35">
+        <v>1</v>
+      </c>
+      <c r="F23" s="35">
+        <v>1</v>
+      </c>
+      <c r="G23" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="34">
+        <v>1</v>
+      </c>
+      <c r="J23" s="34">
+        <v>1</v>
+      </c>
+      <c r="K23" s="34">
+        <v>0</v>
+      </c>
+      <c r="L23" s="34">
+        <v>0</v>
+      </c>
+      <c r="M23" s="34">
+        <v>0</v>
+      </c>
+      <c r="N23" s="34">
+        <v>0</v>
+      </c>
+      <c r="O23" s="34">
+        <v>0</v>
+      </c>
+      <c r="P23" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="34">
+        <v>1</v>
+      </c>
+      <c r="R23" s="34">
+        <v>0</v>
+      </c>
+      <c r="S23" s="34">
+        <v>0</v>
+      </c>
+      <c r="T23" s="34">
+        <v>0</v>
+      </c>
+      <c r="U23" s="34">
+        <v>0</v>
+      </c>
+      <c r="V23" s="34">
+        <v>0</v>
+      </c>
+      <c r="W23" s="34">
+        <v>0</v>
+      </c>
+      <c r="X23" s="34">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="34">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="34">
+        <v>2</v>
+      </c>
+      <c r="AC23" s="34">
+        <v>4</v>
+      </c>
+      <c r="AD23" s="34">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE23" s="34">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="34">
+        <v>2</v>
+      </c>
+      <c r="AG23" s="34">
+        <v>1.2777777777777777</v>
+      </c>
     </row>
-    <row r="24" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="37"/>
-      <c r="Y24" s="38"/>
+    <row r="24" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="35">
+        <v>25</v>
+      </c>
+      <c r="D24" s="35">
+        <v>1</v>
+      </c>
+      <c r="E24" s="35">
+        <v>0</v>
+      </c>
+      <c r="F24" s="35">
+        <v>2</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="34">
+        <v>3</v>
+      </c>
+      <c r="J24" s="34">
+        <v>1</v>
+      </c>
+      <c r="K24" s="34">
+        <v>1</v>
+      </c>
+      <c r="L24" s="34">
+        <v>1</v>
+      </c>
+      <c r="M24" s="34">
+        <v>0</v>
+      </c>
+      <c r="N24" s="34">
+        <v>1</v>
+      </c>
+      <c r="O24" s="34">
+        <v>1</v>
+      </c>
+      <c r="P24" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="34">
+        <v>1</v>
+      </c>
+      <c r="R24" s="34">
+        <v>0</v>
+      </c>
+      <c r="S24" s="34">
+        <v>0</v>
+      </c>
+      <c r="T24" s="34">
+        <v>0</v>
+      </c>
+      <c r="U24" s="34">
+        <v>0</v>
+      </c>
+      <c r="V24" s="34">
+        <v>0</v>
+      </c>
+      <c r="W24" s="34">
+        <v>0</v>
+      </c>
+      <c r="X24" s="34">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="38">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="34">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="34">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="34">
+        <v>7</v>
+      </c>
+      <c r="AD24" s="34">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE24" s="34">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="34">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="34">
+        <v>2.0555555555555558</v>
+      </c>
+      <c r="AH24" s="34" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="25" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="37"/>
-      <c r="Y25" s="38"/>
+    <row r="25" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="35">
+        <v>26</v>
+      </c>
+      <c r="D25" s="35">
+        <v>1</v>
+      </c>
+      <c r="E25" s="35">
+        <v>0</v>
+      </c>
+      <c r="F25" s="35">
+        <v>2</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="34">
+        <v>2</v>
+      </c>
+      <c r="J25" s="34">
+        <v>1</v>
+      </c>
+      <c r="K25" s="34">
+        <v>1</v>
+      </c>
+      <c r="L25" s="34">
+        <v>1</v>
+      </c>
+      <c r="M25" s="34">
+        <v>1</v>
+      </c>
+      <c r="N25" s="34">
+        <v>1</v>
+      </c>
+      <c r="O25" s="34">
+        <v>1</v>
+      </c>
+      <c r="P25" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="34">
+        <v>0</v>
+      </c>
+      <c r="R25" s="34">
+        <v>1</v>
+      </c>
+      <c r="S25" s="34">
+        <v>0</v>
+      </c>
+      <c r="T25" s="34">
+        <v>0</v>
+      </c>
+      <c r="U25" s="34">
+        <v>0</v>
+      </c>
+      <c r="V25" s="34">
+        <v>0</v>
+      </c>
+      <c r="W25" s="34">
+        <v>0</v>
+      </c>
+      <c r="X25" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="34">
+        <v>6</v>
+      </c>
+      <c r="AA25" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="34">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="34">
+        <v>8</v>
+      </c>
+      <c r="AD25" s="34">
+        <v>5</v>
+      </c>
+      <c r="AE25" s="34">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="34">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="34">
+        <v>2.3333333333333335</v>
+      </c>
     </row>
-    <row r="26" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="37"/>
-      <c r="Y26" s="38"/>
+    <row r="26" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="35">
+        <v>27</v>
+      </c>
+      <c r="D26" s="35">
+        <v>1</v>
+      </c>
+      <c r="E26" s="35">
+        <v>1</v>
+      </c>
+      <c r="F26" s="35">
+        <v>2</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="34">
+        <v>3</v>
+      </c>
+      <c r="J26" s="34">
+        <v>1</v>
+      </c>
+      <c r="K26" s="34">
+        <v>1</v>
+      </c>
+      <c r="L26" s="34">
+        <v>1</v>
+      </c>
+      <c r="M26" s="34">
+        <v>1</v>
+      </c>
+      <c r="N26" s="34">
+        <v>1</v>
+      </c>
+      <c r="O26" s="34">
+        <v>0</v>
+      </c>
+      <c r="P26" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="34">
+        <v>0</v>
+      </c>
+      <c r="R26" s="34">
+        <v>1</v>
+      </c>
+      <c r="S26" s="34">
+        <v>0</v>
+      </c>
+      <c r="T26" s="34">
+        <v>0</v>
+      </c>
+      <c r="U26" s="34">
+        <v>1</v>
+      </c>
+      <c r="V26" s="34">
+        <v>1</v>
+      </c>
+      <c r="W26" s="34">
+        <v>0</v>
+      </c>
+      <c r="X26" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="34">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="34">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="34">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="34">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE26" s="34">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="34">
+        <v>3</v>
+      </c>
+      <c r="AG26" s="34">
+        <v>2.7222222222222228</v>
+      </c>
     </row>
-    <row r="27" spans="2:25" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="Y27" s="38"/>
-    </row>
-    <row r="28" spans="2:25" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:25" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="2:25" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="2:25" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:25" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="33" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="34" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="35" ht="14.4" x14ac:dyDescent="0.3"/>
@@ -3469,201 +4406,161 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+    <row r="3" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="35">
-        <v>1</v>
-      </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="36" t="s">
+      <c r="C3" s="15">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="37"/>
-      <c r="Y3" s="38"/>
+      <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+    <row r="4" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="15">
         <v>9</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="37"/>
-      <c r="Y4" s="38"/>
+      <c r="H4" s="27"/>
     </row>
-    <row r="5" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="15">
         <v>8</v>
       </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="37"/>
-      <c r="N5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
+      <c r="H5" s="27"/>
+      <c r="N5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
     </row>
-    <row r="6" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
+    <row r="6" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="15">
         <v>11</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="Y6" s="38"/>
+      <c r="H6" s="27"/>
     </row>
-    <row r="7" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+    <row r="7" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="15">
         <v>7</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="Y7" s="38"/>
+      <c r="H7" s="27"/>
     </row>
-    <row r="8" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
+    <row r="8" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="15">
         <v>19</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="37"/>
-      <c r="Y8" s="38"/>
+      <c r="H8" s="27"/>
     </row>
-    <row r="9" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+    <row r="9" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="15">
         <v>5</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="37"/>
-      <c r="Y9" s="38"/>
+      <c r="H9" s="27"/>
     </row>
-    <row r="10" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
+    <row r="10" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="15">
         <v>25</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="Y10" s="38"/>
+      <c r="H10" s="27"/>
     </row>
-    <row r="11" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+    <row r="11" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="15">
         <v>27</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="37"/>
-      <c r="Y11" s="38"/>
+      <c r="H11" s="27"/>
     </row>
-    <row r="12" spans="1:35" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+    <row r="12" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="15">
         <v>26</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="37"/>
-      <c r="Y12" s="38"/>
+      <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:35" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:35" ht="14.4" x14ac:dyDescent="0.3"/>

--- a/Raw/redo_uws_google.xlsx
+++ b/Raw/redo_uws_google.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katia\Desktop\STAGE\M1\Travail\Stage_M1_UWS\Raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c0c9e545cc4bad76/Bureau/STAGE/Stage_M1_UWS/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB3C6BE-A2F7-402B-BC05-7D55094140A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BB395F11-BC3A-4796-B35A-8F2D9D0895E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5269F1C1-1E5F-471F-93F0-690A5DCC00C7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
   </bookViews>
   <sheets>
     <sheet name="19th" sheetId="5" r:id="rId1"/>
     <sheet name="7th" sheetId="7" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="103">
   <si>
     <r>
       <t>Structural complexity</t>
@@ -677,15 +678,24 @@
     <t>Odd</t>
   </si>
   <si>
+    <t>June 2021</t>
+  </si>
+  <si>
     <t>19e</t>
   </si>
   <si>
     <t>48.87939, 2.38529</t>
   </si>
   <si>
+    <t>March 2023</t>
+  </si>
+  <si>
     <t>48.87988, 2.39167</t>
   </si>
   <si>
+    <t>August 2022</t>
+  </si>
+  <si>
     <t>48.88012, 2.3985</t>
   </si>
   <si>
@@ -698,12 +708,18 @@
     <t>/</t>
   </si>
   <si>
+    <t>June 2024</t>
+  </si>
+  <si>
     <t>48.88568, 2.38995</t>
   </si>
   <si>
     <t>Even</t>
   </si>
   <si>
+    <t>October 2025</t>
+  </si>
+  <si>
     <t>48.89055, 2.38671</t>
   </si>
   <si>
@@ -713,6 +729,12 @@
     <t>Tram</t>
   </si>
   <si>
+    <t>July 2025</t>
+  </si>
+  <si>
+    <t>48.89728, 2.39237</t>
+  </si>
+  <si>
     <t>48.89002, 2.39686</t>
   </si>
   <si>
@@ -722,12 +744,18 @@
     <t>48.87811, 2.38777</t>
   </si>
   <si>
+    <t>November 2022</t>
+  </si>
+  <si>
     <t>48.87679, 2.38535</t>
   </si>
   <si>
     <t>48.87498, 2.38588</t>
   </si>
   <si>
+    <t>48.88622, 2.3799</t>
+  </si>
+  <si>
     <t>7e</t>
   </si>
   <si>
@@ -770,55 +798,64 @@
     <t>Parc</t>
   </si>
   <si>
-    <t>June 2021</t>
-  </si>
-  <si>
-    <t>March 2023</t>
-  </si>
-  <si>
-    <t>August 2022</t>
-  </si>
-  <si>
-    <t>June 2024</t>
-  </si>
-  <si>
-    <t>October 2025</t>
-  </si>
-  <si>
-    <t>July 2025</t>
-  </si>
-  <si>
-    <t>48.89728, 2.39237</t>
-  </si>
-  <si>
-    <t>November 2022</t>
-  </si>
-  <si>
-    <t>(Even)</t>
+    <t>Tandou</t>
+  </si>
+  <si>
+    <t>March 2026</t>
+  </si>
+  <si>
+    <t>48.88326, 2.37388</t>
+  </si>
+  <si>
+    <t>Lally</t>
+  </si>
+  <si>
+    <t>48.86175, 2.3045</t>
+  </si>
+  <si>
+    <t>cognac</t>
+  </si>
+  <si>
+    <t>48.8482, 2.29692</t>
+  </si>
+  <si>
+    <t>commerce</t>
+  </si>
+  <si>
+    <t>15e</t>
+  </si>
+  <si>
+    <t>48.85862, 2.32703</t>
+  </si>
+  <si>
+    <t>verneuil</t>
+  </si>
+  <si>
+    <t>Montalembert</t>
+  </si>
+  <si>
+    <t>48.85674, 2.32744</t>
+  </si>
+  <si>
+    <t>48.8608, 2.32009</t>
+  </si>
+  <si>
+    <t>Courty</t>
   </si>
   <si>
     <t>May 2023</t>
   </si>
   <si>
+    <t>June 2022</t>
+  </si>
+  <si>
+    <t>April 2024</t>
+  </si>
+  <si>
+    <t>September 2025</t>
+  </si>
+  <si>
     <t>July 2022</t>
-  </si>
-  <si>
-    <t>April 2024</t>
-  </si>
-  <si>
-    <t>Vegetated areas but also a lot of spontaneous vegetation ! So there are the advantages of spontaneous vegetation as well, like saying unplanted species</t>
-  </si>
-  <si>
-    <t>June 2022</t>
-  </si>
-  <si>
-    <t>September 2025</t>
-  </si>
-  <si>
-    <t>(Odd)</t>
-  </si>
-  <si>
-    <t>Terre-plein semblant non piéton (marche difficile), mais avec des bancs… donc ok</t>
   </si>
   <si>
     <t>May 2022</t>
@@ -1007,7 +1044,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,7 +1090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1136,6 +1173,18 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1153,21 +1202,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1509,50 +1543,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD31EF42-CD6F-4144-8202-D50E1E1A911D}">
   <dimension ref="A1:AI58"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="15" customWidth="1"/>
-    <col min="3" max="6" width="23.5546875" style="15" customWidth="1"/>
-    <col min="7" max="8" width="23.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" style="1" customWidth="1"/>
-    <col min="10" max="17" width="18.44140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="24.6640625" style="1" customWidth="1"/>
-    <col min="19" max="24" width="18.44140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="18.44140625" style="22" customWidth="1"/>
-    <col min="26" max="33" width="15.6640625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="37.109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="29.6640625" style="1" customWidth="1"/>
-    <col min="36" max="16384" width="8.6640625" style="1"/>
+    <col min="3" max="6" width="23.5703125" style="15" customWidth="1"/>
+    <col min="7" max="8" width="23.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" customWidth="1"/>
+    <col min="10" max="17" width="18.42578125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="24.7109375" style="1" customWidth="1"/>
+    <col min="19" max="24" width="18.42578125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="18.42578125" style="22" customWidth="1"/>
+    <col min="26" max="33" width="15.7109375" style="1" customWidth="1"/>
+    <col min="34" max="34" width="37.140625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="29.7109375" style="1" customWidth="1"/>
+    <col min="36" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
+    <row r="1" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
       <c r="Z1" s="13"/>
       <c r="AA1" s="13"/>
     </row>
-    <row r="2" spans="1:35" s="3" customFormat="1" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" s="3" customFormat="1" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>3</v>
       </c>
@@ -1659,7 +1693,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>38</v>
       </c>
@@ -1682,7 +1716,7 @@
         <v>41</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="I3" s="21">
         <v>3.5</v>
@@ -1768,12 +1802,12 @@
         <v>2.7777777777777772</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="15">
         <v>8</v>
@@ -1791,7 +1825,7 @@
         <v>41</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1">
         <v>1.5</v>
@@ -1845,19 +1879,19 @@
         <v>0</v>
       </c>
       <c r="Z4" s="1">
-        <f t="shared" ref="Z4:Z16" si="0">SUM(J4:O4)</f>
+        <f t="shared" ref="Z4:Z18" si="0">SUM(J4:O4)</f>
         <v>2</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" ref="AA4:AA16" si="1">SUM(P4:T4)</f>
+        <f t="shared" ref="AA4:AA18" si="1">SUM(P4:T4)</f>
         <v>0</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" ref="AB4:AB16" si="2">SUM(U4:Y4)</f>
+        <f t="shared" ref="AB4:AB18" si="2">SUM(U4:Y4)</f>
         <v>2</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" ref="AC4:AC16" si="3">SUM(Z4:AB4)</f>
+        <f t="shared" ref="AC4:AC18" si="3">SUM(Z4:AB4)</f>
         <v>4</v>
       </c>
       <c r="AD4" s="1">
@@ -1878,12 +1912,12 @@
       </c>
       <c r="AI4" s="23"/>
     </row>
-    <row r="5" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" s="15">
         <v>11</v>
@@ -1901,7 +1935,7 @@
         <v>41</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -1987,12 +2021,12 @@
         <v>1.8888888888888886</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" s="15">
         <v>26</v>
@@ -2010,7 +2044,7 @@
         <v>41</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
@@ -2096,12 +2130,12 @@
         <v>1.2222222222222221</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C7" s="15">
         <v>17</v>
@@ -2119,7 +2153,7 @@
         <v>41</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="I7" s="1">
         <v>3</v>
@@ -2206,12 +2240,12 @@
       </c>
       <c r="AI7" s="24"/>
     </row>
-    <row r="8" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C8" s="15">
         <v>30</v>
@@ -2226,10 +2260,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="I8" s="1">
         <v>3.5</v>
@@ -2316,12 +2350,12 @@
       </c>
       <c r="AI8" s="23"/>
     </row>
-    <row r="9" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C9" s="15">
         <v>20</v>
@@ -2336,10 +2370,10 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -2426,12 +2460,12 @@
       </c>
       <c r="AI9" s="25"/>
     </row>
-    <row r="10" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C10" s="15">
         <v>2</v>
@@ -2449,7 +2483,7 @@
         <v>41</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="I10" s="1">
         <v>2</v>
@@ -2536,12 +2570,12 @@
       </c>
       <c r="AI10" s="23"/>
     </row>
-    <row r="11" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C11" s="15">
         <v>21</v>
@@ -2556,10 +2590,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="I11" s="1">
         <v>4</v>
@@ -2645,12 +2679,12 @@
         <v>3.3888888888888893</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C12" s="15">
         <v>33</v>
@@ -2665,10 +2699,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="I12" s="1">
         <v>3</v>
@@ -2754,12 +2788,12 @@
         <v>2.4444444444444442</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C13" s="15">
         <v>27</v>
@@ -2774,10 +2808,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I13" s="1">
         <v>0.5</v>
@@ -2863,12 +2897,12 @@
         <v>1.2777777777777777</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C14" s="15">
         <v>6</v>
@@ -2883,10 +2917,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="I14" s="1">
         <v>0.5</v>
@@ -2972,12 +3006,12 @@
         <v>1.7777777777777777</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -2995,7 +3029,7 @@
         <v>41</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="I15" s="1">
         <v>3</v>
@@ -3081,12 +3115,12 @@
         <v>3.1111111111111107</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C16" s="15">
         <v>1</v>
@@ -3104,7 +3138,7 @@
         <v>41</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I16" s="1">
         <v>0.5</v>
@@ -3190,1054 +3224,286 @@
         <v>1.2777777777777777</v>
       </c>
     </row>
-    <row r="17" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="35">
-        <v>1</v>
-      </c>
-      <c r="D17" s="35">
-        <v>1</v>
-      </c>
-      <c r="E17" s="35">
-        <v>0</v>
-      </c>
-      <c r="F17" s="35">
-        <v>2</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="37" t="s">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="34">
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="1">
+        <v>4</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>1</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1">
+        <v>1</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AA17" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB17" s="1">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J17" s="34">
-        <v>1</v>
-      </c>
-      <c r="K17" s="34">
-        <v>1</v>
-      </c>
-      <c r="L17" s="34">
-        <v>1</v>
-      </c>
-      <c r="M17" s="34">
-        <v>1</v>
-      </c>
-      <c r="N17" s="34">
-        <v>1</v>
-      </c>
-      <c r="O17" s="34">
-        <v>1</v>
-      </c>
-      <c r="P17" s="34">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="34">
-        <v>0</v>
-      </c>
-      <c r="R17" s="34">
-        <v>0</v>
-      </c>
-      <c r="S17" s="34">
-        <v>0</v>
-      </c>
-      <c r="T17" s="34">
-        <v>0</v>
-      </c>
-      <c r="U17" s="34">
-        <v>1</v>
-      </c>
-      <c r="V17" s="34">
-        <v>1</v>
-      </c>
-      <c r="W17" s="34">
-        <v>0</v>
-      </c>
-      <c r="X17" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="34">
-        <v>6</v>
-      </c>
-      <c r="AA17" s="34">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="34">
+      <c r="AC17" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="AD17" s="1">
+        <f t="shared" ref="AD17:AD18" si="8" xml:space="preserve"> Z17/6*5</f>
+        <v>5</v>
+      </c>
+      <c r="AE17" s="1">
+        <f t="shared" ref="AE17:AE18" si="9">AA17/5*5</f>
+        <v>1</v>
+      </c>
+      <c r="AF17" s="1">
+        <f t="shared" ref="AF17:AF18" si="10" xml:space="preserve"> AB17/5*5</f>
         <v>3</v>
       </c>
-      <c r="AC17" s="34">
-        <v>10</v>
-      </c>
-      <c r="AD17" s="34">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="34">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="34">
+      <c r="AG17" s="1">
+        <f t="shared" ref="AG17:AG18" si="11">SUM(AD17:AF17)/3</f>
         <v>3</v>
       </c>
-      <c r="AG17" s="34">
-        <v>3</v>
-      </c>
     </row>
-    <row r="18" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="35">
-        <v>5</v>
-      </c>
-      <c r="D18" s="35">
-        <v>0</v>
-      </c>
-      <c r="E18" s="35">
-        <v>0</v>
-      </c>
-      <c r="F18" s="35">
-        <v>2</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="37" t="s">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="15">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="34">
-        <v>1</v>
-      </c>
-      <c r="J18" s="34">
-        <v>1</v>
-      </c>
-      <c r="K18" s="34">
-        <v>0</v>
-      </c>
-      <c r="L18" s="34">
-        <v>0</v>
-      </c>
-      <c r="M18" s="34">
-        <v>1</v>
-      </c>
-      <c r="N18" s="34">
-        <v>1</v>
-      </c>
-      <c r="O18" s="34">
-        <v>0</v>
-      </c>
-      <c r="P18" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="34">
-        <v>0</v>
-      </c>
-      <c r="R18" s="34">
-        <v>0</v>
-      </c>
-      <c r="S18" s="34">
-        <v>0</v>
-      </c>
-      <c r="T18" s="34">
-        <v>0</v>
-      </c>
-      <c r="U18" s="34">
-        <v>0</v>
-      </c>
-      <c r="V18" s="34">
-        <v>0</v>
-      </c>
-      <c r="W18" s="34">
-        <v>0</v>
-      </c>
-      <c r="X18" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="34">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="34">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="34">
+      <c r="I18" s="1">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>1</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA18" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB18" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC18" s="1">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="AD18" s="34">
-        <v>2.5</v>
-      </c>
-      <c r="AE18" s="34">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="34">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="34">
-        <v>1.1666666666666667</v>
+      <c r="AD18" s="1">
+        <f t="shared" si="8"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE18" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AF18" s="1">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AG18" s="1">
+        <f t="shared" si="11"/>
+        <v>1.2777777777777777</v>
       </c>
     </row>
-    <row r="19" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="35">
-        <v>7</v>
-      </c>
-      <c r="D19" s="35">
-        <v>0</v>
-      </c>
-      <c r="E19" s="35">
-        <v>0</v>
-      </c>
-      <c r="F19" s="35">
-        <v>1</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="34">
-        <v>0</v>
-      </c>
-      <c r="J19" s="34">
-        <v>1</v>
-      </c>
-      <c r="K19" s="34">
-        <v>0</v>
-      </c>
-      <c r="L19" s="34">
-        <v>0</v>
-      </c>
-      <c r="M19" s="34">
-        <v>0</v>
-      </c>
-      <c r="N19" s="38">
-        <v>0</v>
-      </c>
-      <c r="O19" s="34">
-        <v>0</v>
-      </c>
-      <c r="P19" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="38">
-        <v>1</v>
-      </c>
-      <c r="R19" s="38">
-        <v>0</v>
-      </c>
-      <c r="S19" s="34">
-        <v>0</v>
-      </c>
-      <c r="T19" s="34">
-        <v>0</v>
-      </c>
-      <c r="U19" s="38">
-        <v>0</v>
-      </c>
-      <c r="V19" s="34">
-        <v>0</v>
-      </c>
-      <c r="W19" s="38">
-        <v>0</v>
-      </c>
-      <c r="X19" s="38">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="34">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="34">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="34">
-        <v>2</v>
-      </c>
-      <c r="AC19" s="34">
-        <v>4</v>
-      </c>
-      <c r="AD19" s="34">
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="AE19" s="34">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="34">
-        <v>2</v>
-      </c>
-      <c r="AG19" s="34">
-        <v>1.2777777777777777</v>
-      </c>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H19" s="27"/>
+      <c r="N19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="22"/>
     </row>
-    <row r="20" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="35">
-        <v>8</v>
-      </c>
-      <c r="D20" s="35">
-        <v>1</v>
-      </c>
-      <c r="E20" s="35">
-        <v>0</v>
-      </c>
-      <c r="F20" s="35">
-        <v>2</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="I20" s="34">
-        <v>4</v>
-      </c>
-      <c r="J20" s="34">
-        <v>1</v>
-      </c>
-      <c r="K20" s="34">
-        <v>1</v>
-      </c>
-      <c r="L20" s="34">
-        <v>0</v>
-      </c>
-      <c r="M20" s="34">
-        <v>1</v>
-      </c>
-      <c r="N20" s="34">
-        <v>1</v>
-      </c>
-      <c r="O20" s="34">
-        <v>1</v>
-      </c>
-      <c r="P20" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="34">
-        <v>1</v>
-      </c>
-      <c r="R20" s="34">
-        <v>1</v>
-      </c>
-      <c r="S20" s="34">
-        <v>0</v>
-      </c>
-      <c r="T20" s="34">
-        <v>0</v>
-      </c>
-      <c r="U20" s="34">
-        <v>1</v>
-      </c>
-      <c r="V20" s="34">
-        <v>1</v>
-      </c>
-      <c r="W20" s="34">
-        <v>0</v>
-      </c>
-      <c r="X20" s="34">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="34">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="34">
-        <v>2</v>
-      </c>
-      <c r="AB20" s="34">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="34">
-        <v>11</v>
-      </c>
-      <c r="AD20" s="34">
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE20" s="34">
-        <v>2</v>
-      </c>
-      <c r="AF20" s="34">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="34">
-        <v>3.3888888888888893</v>
-      </c>
-      <c r="AH20" s="34" t="s">
-        <v>85</v>
-      </c>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H20" s="27"/>
     </row>
-    <row r="21" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="35">
-        <v>9</v>
-      </c>
-      <c r="D21" s="35">
-        <v>0</v>
-      </c>
-      <c r="E21" s="35">
-        <v>0</v>
-      </c>
-      <c r="F21" s="35">
-        <v>2</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="I21" s="34">
-        <v>1</v>
-      </c>
-      <c r="J21" s="34">
-        <v>1</v>
-      </c>
-      <c r="K21" s="34">
-        <v>0</v>
-      </c>
-      <c r="L21" s="34">
-        <v>1</v>
-      </c>
-      <c r="M21" s="34">
-        <v>1</v>
-      </c>
-      <c r="N21" s="34">
-        <v>1</v>
-      </c>
-      <c r="O21" s="34">
-        <v>0</v>
-      </c>
-      <c r="P21" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="34">
-        <v>0</v>
-      </c>
-      <c r="R21" s="34">
-        <v>0</v>
-      </c>
-      <c r="S21" s="34">
-        <v>0</v>
-      </c>
-      <c r="T21" s="34">
-        <v>0</v>
-      </c>
-      <c r="U21" s="34">
-        <v>0</v>
-      </c>
-      <c r="V21" s="34">
-        <v>1</v>
-      </c>
-      <c r="W21" s="34">
-        <v>0</v>
-      </c>
-      <c r="X21" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="34">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="34">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="34">
-        <v>6</v>
-      </c>
-      <c r="AD21" s="34">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="AE21" s="34">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="34">
-        <v>2</v>
-      </c>
-      <c r="AG21" s="34">
-        <v>1.7777777777777777</v>
-      </c>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="35">
-        <v>11</v>
-      </c>
-      <c r="D22" s="35">
-        <v>0</v>
-      </c>
-      <c r="E22" s="35">
-        <v>1</v>
-      </c>
-      <c r="F22" s="35">
-        <v>1</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="I22" s="34">
-        <v>1</v>
-      </c>
-      <c r="J22" s="34">
-        <v>1</v>
-      </c>
-      <c r="K22" s="34">
-        <v>0</v>
-      </c>
-      <c r="L22" s="34">
-        <v>0</v>
-      </c>
-      <c r="M22" s="34">
-        <v>0</v>
-      </c>
-      <c r="N22" s="34">
-        <v>0</v>
-      </c>
-      <c r="O22" s="34">
-        <v>0</v>
-      </c>
-      <c r="P22" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="34">
-        <v>1</v>
-      </c>
-      <c r="R22" s="34">
-        <v>0</v>
-      </c>
-      <c r="S22" s="34">
-        <v>0</v>
-      </c>
-      <c r="T22" s="34">
-        <v>0</v>
-      </c>
-      <c r="U22" s="34">
-        <v>0</v>
-      </c>
-      <c r="V22" s="34">
-        <v>0</v>
-      </c>
-      <c r="W22" s="34">
-        <v>0</v>
-      </c>
-      <c r="X22" s="34">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="34">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="34">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="34">
-        <v>2</v>
-      </c>
-      <c r="AC22" s="34">
-        <v>4</v>
-      </c>
-      <c r="AD22" s="34">
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="AE22" s="34">
-        <v>1</v>
-      </c>
-      <c r="AF22" s="34">
-        <v>2</v>
-      </c>
-      <c r="AG22" s="34">
-        <v>1.2777777777777777</v>
-      </c>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H22" s="27"/>
     </row>
-    <row r="23" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="35">
-        <v>19</v>
-      </c>
-      <c r="D23" s="35">
-        <v>0</v>
-      </c>
-      <c r="E23" s="35">
-        <v>1</v>
-      </c>
-      <c r="F23" s="35">
-        <v>1</v>
-      </c>
-      <c r="G23" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" s="34">
-        <v>1</v>
-      </c>
-      <c r="J23" s="34">
-        <v>1</v>
-      </c>
-      <c r="K23" s="34">
-        <v>0</v>
-      </c>
-      <c r="L23" s="34">
-        <v>0</v>
-      </c>
-      <c r="M23" s="34">
-        <v>0</v>
-      </c>
-      <c r="N23" s="34">
-        <v>0</v>
-      </c>
-      <c r="O23" s="34">
-        <v>0</v>
-      </c>
-      <c r="P23" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="34">
-        <v>1</v>
-      </c>
-      <c r="R23" s="34">
-        <v>0</v>
-      </c>
-      <c r="S23" s="34">
-        <v>0</v>
-      </c>
-      <c r="T23" s="34">
-        <v>0</v>
-      </c>
-      <c r="U23" s="34">
-        <v>0</v>
-      </c>
-      <c r="V23" s="34">
-        <v>0</v>
-      </c>
-      <c r="W23" s="34">
-        <v>0</v>
-      </c>
-      <c r="X23" s="34">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="34">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="34">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="34">
-        <v>2</v>
-      </c>
-      <c r="AC23" s="34">
-        <v>4</v>
-      </c>
-      <c r="AD23" s="34">
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="AE23" s="34">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="34">
-        <v>2</v>
-      </c>
-      <c r="AG23" s="34">
-        <v>1.2777777777777777</v>
-      </c>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="35">
-        <v>25</v>
-      </c>
-      <c r="D24" s="35">
-        <v>1</v>
-      </c>
-      <c r="E24" s="35">
-        <v>0</v>
-      </c>
-      <c r="F24" s="35">
-        <v>2</v>
-      </c>
-      <c r="G24" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="34">
-        <v>3</v>
-      </c>
-      <c r="J24" s="34">
-        <v>1</v>
-      </c>
-      <c r="K24" s="34">
-        <v>1</v>
-      </c>
-      <c r="L24" s="34">
-        <v>1</v>
-      </c>
-      <c r="M24" s="34">
-        <v>0</v>
-      </c>
-      <c r="N24" s="34">
-        <v>1</v>
-      </c>
-      <c r="O24" s="34">
-        <v>1</v>
-      </c>
-      <c r="P24" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="34">
-        <v>1</v>
-      </c>
-      <c r="R24" s="34">
-        <v>0</v>
-      </c>
-      <c r="S24" s="34">
-        <v>0</v>
-      </c>
-      <c r="T24" s="34">
-        <v>0</v>
-      </c>
-      <c r="U24" s="34">
-        <v>0</v>
-      </c>
-      <c r="V24" s="34">
-        <v>0</v>
-      </c>
-      <c r="W24" s="34">
-        <v>0</v>
-      </c>
-      <c r="X24" s="34">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="38">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="34">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="34">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="34">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="34">
-        <v>7</v>
-      </c>
-      <c r="AD24" s="34">
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE24" s="34">
-        <v>1</v>
-      </c>
-      <c r="AF24" s="34">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="34">
-        <v>2.0555555555555558</v>
-      </c>
-      <c r="AH24" s="34" t="s">
-        <v>89</v>
-      </c>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H24" s="27"/>
     </row>
-    <row r="25" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="35">
-        <v>26</v>
-      </c>
-      <c r="D25" s="35">
-        <v>1</v>
-      </c>
-      <c r="E25" s="35">
-        <v>0</v>
-      </c>
-      <c r="F25" s="35">
-        <v>2</v>
-      </c>
-      <c r="G25" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="I25" s="34">
-        <v>2</v>
-      </c>
-      <c r="J25" s="34">
-        <v>1</v>
-      </c>
-      <c r="K25" s="34">
-        <v>1</v>
-      </c>
-      <c r="L25" s="34">
-        <v>1</v>
-      </c>
-      <c r="M25" s="34">
-        <v>1</v>
-      </c>
-      <c r="N25" s="34">
-        <v>1</v>
-      </c>
-      <c r="O25" s="34">
-        <v>1</v>
-      </c>
-      <c r="P25" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="34">
-        <v>0</v>
-      </c>
-      <c r="R25" s="34">
-        <v>1</v>
-      </c>
-      <c r="S25" s="34">
-        <v>0</v>
-      </c>
-      <c r="T25" s="34">
-        <v>0</v>
-      </c>
-      <c r="U25" s="34">
-        <v>0</v>
-      </c>
-      <c r="V25" s="34">
-        <v>0</v>
-      </c>
-      <c r="W25" s="34">
-        <v>0</v>
-      </c>
-      <c r="X25" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="34">
-        <v>6</v>
-      </c>
-      <c r="AA25" s="34">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="34">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="34">
-        <v>8</v>
-      </c>
-      <c r="AD25" s="34">
-        <v>5</v>
-      </c>
-      <c r="AE25" s="34">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="34">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="34">
-        <v>2.3333333333333335</v>
-      </c>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:34" s="34" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="35">
-        <v>27</v>
-      </c>
-      <c r="D26" s="35">
-        <v>1</v>
-      </c>
-      <c r="E26" s="35">
-        <v>1</v>
-      </c>
-      <c r="F26" s="35">
-        <v>2</v>
-      </c>
-      <c r="G26" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="I26" s="34">
-        <v>3</v>
-      </c>
-      <c r="J26" s="34">
-        <v>1</v>
-      </c>
-      <c r="K26" s="34">
-        <v>1</v>
-      </c>
-      <c r="L26" s="34">
-        <v>1</v>
-      </c>
-      <c r="M26" s="34">
-        <v>1</v>
-      </c>
-      <c r="N26" s="34">
-        <v>1</v>
-      </c>
-      <c r="O26" s="34">
-        <v>0</v>
-      </c>
-      <c r="P26" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="34">
-        <v>0</v>
-      </c>
-      <c r="R26" s="34">
-        <v>1</v>
-      </c>
-      <c r="S26" s="34">
-        <v>0</v>
-      </c>
-      <c r="T26" s="34">
-        <v>0</v>
-      </c>
-      <c r="U26" s="34">
-        <v>1</v>
-      </c>
-      <c r="V26" s="34">
-        <v>1</v>
-      </c>
-      <c r="W26" s="34">
-        <v>0</v>
-      </c>
-      <c r="X26" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="38">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="34">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="34">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="34">
-        <v>3</v>
-      </c>
-      <c r="AC26" s="34">
-        <v>9</v>
-      </c>
-      <c r="AD26" s="34">
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE26" s="34">
-        <v>1</v>
-      </c>
-      <c r="AF26" s="34">
-        <v>3</v>
-      </c>
-      <c r="AG26" s="34">
-        <v>2.7222222222222228</v>
-      </c>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="H26" s="27"/>
     </row>
-    <row r="27" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25"/>
+    <row r="33" x14ac:dyDescent="0.25"/>
+    <row r="34" x14ac:dyDescent="0.25"/>
+    <row r="35" x14ac:dyDescent="0.25"/>
+    <row r="36" x14ac:dyDescent="0.25"/>
+    <row r="37" x14ac:dyDescent="0.25"/>
+    <row r="38" x14ac:dyDescent="0.25"/>
+    <row r="39" x14ac:dyDescent="0.25"/>
+    <row r="40" x14ac:dyDescent="0.25"/>
+    <row r="41" x14ac:dyDescent="0.25"/>
+    <row r="42" x14ac:dyDescent="0.25"/>
+    <row r="43" x14ac:dyDescent="0.25"/>
+    <row r="44" x14ac:dyDescent="0.25"/>
+    <row r="45" x14ac:dyDescent="0.25"/>
+    <row r="46" x14ac:dyDescent="0.25"/>
+    <row r="47" x14ac:dyDescent="0.25"/>
+    <row r="48" x14ac:dyDescent="0.25"/>
+    <row r="49" x14ac:dyDescent="0.25"/>
+    <row r="50" x14ac:dyDescent="0.25"/>
+    <row r="51" x14ac:dyDescent="0.25"/>
+    <row r="52" x14ac:dyDescent="0.25"/>
+    <row r="53" x14ac:dyDescent="0.25"/>
+    <row r="54" x14ac:dyDescent="0.25"/>
+    <row r="55" x14ac:dyDescent="0.25"/>
+    <row r="56" x14ac:dyDescent="0.25"/>
+    <row r="57" x14ac:dyDescent="0.25"/>
+    <row r="58" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="J1:O1"/>
@@ -4256,50 +3522,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002DCE7B-7CF1-4EEB-8F33-F36E592CD7EE}">
   <dimension ref="A1:AI44"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="15" customWidth="1"/>
-    <col min="3" max="6" width="23.5546875" style="15" customWidth="1"/>
-    <col min="7" max="8" width="23.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" style="1" customWidth="1"/>
-    <col min="10" max="17" width="18.44140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="24.6640625" style="1" customWidth="1"/>
-    <col min="19" max="24" width="18.44140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="18.44140625" style="22" customWidth="1"/>
-    <col min="26" max="33" width="15.6640625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="37.109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="29.6640625" style="1" customWidth="1"/>
-    <col min="36" max="16384" width="8.6640625" style="1"/>
+    <col min="3" max="6" width="23.5703125" style="15" customWidth="1"/>
+    <col min="7" max="8" width="23.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" customWidth="1"/>
+    <col min="10" max="17" width="18.42578125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="24.7109375" style="1" customWidth="1"/>
+    <col min="19" max="24" width="18.42578125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="18.42578125" style="22" customWidth="1"/>
+    <col min="26" max="33" width="15.7109375" style="1" customWidth="1"/>
+    <col min="34" max="34" width="37.140625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="29.7109375" style="1" customWidth="1"/>
+    <col min="36" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
+    <row r="1" spans="1:35" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
       <c r="Z1" s="13"/>
       <c r="AA1" s="13"/>
     </row>
-    <row r="2" spans="1:35" s="3" customFormat="1" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" s="3" customFormat="1" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>3</v>
       </c>
@@ -4406,206 +3672,1669 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C3" s="15">
         <v>1</v>
       </c>
+      <c r="D3" s="15">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
+        <v>2</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="27"/>
+        <v>54</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1">
+        <v>1</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1">
+        <f>SUM(J3:O3)</f>
+        <v>5</v>
+      </c>
+      <c r="AA3" s="1">
+        <f>SUM(P3:T3)</f>
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1">
+        <f>SUM(U3:Y3)</f>
+        <v>4</v>
+      </c>
+      <c r="AC3" s="1">
+        <f>SUM(Z3:AB3)</f>
+        <v>10</v>
+      </c>
+      <c r="AD3" s="1">
+        <f xml:space="preserve"> Z3/6*5</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE3" s="1">
+        <f>AA3/5*5</f>
+        <v>1</v>
+      </c>
+      <c r="AF3" s="1">
+        <f xml:space="preserve"> AB3/5*5</f>
+        <v>4</v>
+      </c>
+      <c r="AG3" s="1">
+        <f>SUM(AD3:AF3)/3</f>
+        <v>3.0555555555555558</v>
+      </c>
     </row>
-    <row r="4" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C4" s="15">
         <v>9</v>
       </c>
+      <c r="D4" s="15">
+        <v>1</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
+        <v>2</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="27"/>
+        <v>71</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" ref="Z4:Z16" si="0">SUM(J4:O4)</f>
+        <v>5</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ref="AA4:AA16" si="1">SUM(P4:T4)</f>
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" ref="AB4:AB16" si="2">SUM(U4:Y4)</f>
+        <v>2</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" ref="AC4:AC16" si="3">SUM(Z4:AB4)</f>
+        <v>8</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" ref="AD4:AD16" si="4" xml:space="preserve"> Z4/6*5</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" ref="AE4:AE16" si="5">AA4/5*5</f>
+        <v>1</v>
+      </c>
+      <c r="AF4" s="1">
+        <f t="shared" ref="AF4:AF16" si="6" xml:space="preserve"> AB4/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AG4" s="1">
+        <f t="shared" ref="AG4:AG16" si="7">SUM(AD4:AF4)/3</f>
+        <v>2.3888888888888888</v>
+      </c>
     </row>
-    <row r="5" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C5" s="15">
         <v>8</v>
       </c>
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
+        <v>2</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="27"/>
-      <c r="N5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
+        <v>73</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="22">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="22">
+        <v>1</v>
+      </c>
+      <c r="R5" s="22">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="22">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1">
+        <v>1</v>
+      </c>
+      <c r="W5" s="22">
+        <v>0</v>
+      </c>
+      <c r="X5" s="22">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF5" s="1">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AG5" s="1">
+        <f t="shared" si="7"/>
+        <v>2.8333333333333335</v>
+      </c>
     </row>
-    <row r="6" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C6" s="15">
         <v>11</v>
       </c>
+      <c r="D6" s="15">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
+        <v>1</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="27"/>
+        <v>54</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2777777777777777</v>
+      </c>
     </row>
-    <row r="7" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C7" s="15">
         <v>7</v>
       </c>
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15">
+        <v>1</v>
+      </c>
       <c r="G7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG7" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2777777777777777</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C8" s="15">
         <v>19</v>
       </c>
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="27"/>
+        <v>54</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
+        <v>1</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" si="4"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" si="7"/>
+        <v>1.8888888888888886</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C9" s="15">
         <v>5</v>
       </c>
+      <c r="D9" s="15">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15">
+        <v>2</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="27"/>
+        <v>54</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" si="7"/>
+        <v>2.1666666666666665</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C10" s="15">
         <v>25</v>
       </c>
+      <c r="D10" s="15">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15">
+        <v>2</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="27"/>
+        <v>54</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" si="7"/>
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C11" s="15">
         <v>27</v>
       </c>
+      <c r="D11" s="15">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15">
+        <v>2</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="27"/>
+        <v>54</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" si="4"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG11" s="1">
+        <f t="shared" si="7"/>
+        <v>2.3888888888888888</v>
+      </c>
     </row>
-    <row r="12" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C12" s="15">
         <v>26</v>
       </c>
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15">
+        <v>2</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="27"/>
+        <v>81</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" si="7"/>
+        <v>2.6666666666666665</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="15">
+        <v>1</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="1">
+        <v>3</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>1</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>1</v>
+      </c>
+      <c r="U13" s="1">
+        <v>1</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="AD13" s="1">
+        <f t="shared" si="4"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7222222222222228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="15">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>1</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>1</v>
+      </c>
+      <c r="V14" s="1">
+        <v>1</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="AD14" s="1">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" si="7"/>
+        <v>2.1666666666666665</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>1</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <v>1</v>
+      </c>
+      <c r="U15" s="1">
+        <v>1</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA15" s="1">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AB15" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC15" s="1">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="AD15" s="1">
+        <f t="shared" si="4"/>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AE15" s="1">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AF15" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG15" s="1">
+        <f t="shared" si="7"/>
+        <v>2.4444444444444442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA16" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB16" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AC16" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AD16" s="1">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE16" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF16" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AG16" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2777777777777777</v>
+      </c>
+    </row>
+    <row r="17" x14ac:dyDescent="0.25"/>
+    <row r="18" x14ac:dyDescent="0.25"/>
+    <row r="19" x14ac:dyDescent="0.25"/>
+    <row r="20" x14ac:dyDescent="0.25"/>
+    <row r="21" x14ac:dyDescent="0.25"/>
+    <row r="22" x14ac:dyDescent="0.25"/>
+    <row r="23" x14ac:dyDescent="0.25"/>
+    <row r="24" x14ac:dyDescent="0.25"/>
+    <row r="25" x14ac:dyDescent="0.25"/>
+    <row r="26" x14ac:dyDescent="0.25"/>
+    <row r="27" x14ac:dyDescent="0.25"/>
+    <row r="28" x14ac:dyDescent="0.25"/>
+    <row r="29" x14ac:dyDescent="0.25"/>
+    <row r="30" x14ac:dyDescent="0.25"/>
+    <row r="31" x14ac:dyDescent="0.25"/>
+    <row r="32" x14ac:dyDescent="0.25"/>
+    <row r="33" x14ac:dyDescent="0.25"/>
+    <row r="34" x14ac:dyDescent="0.25"/>
+    <row r="35" x14ac:dyDescent="0.25"/>
+    <row r="36" x14ac:dyDescent="0.25"/>
+    <row r="37" x14ac:dyDescent="0.25"/>
+    <row r="38" x14ac:dyDescent="0.25"/>
+    <row r="39" x14ac:dyDescent="0.25"/>
+    <row r="40" x14ac:dyDescent="0.25"/>
+    <row r="41" x14ac:dyDescent="0.25"/>
+    <row r="42" x14ac:dyDescent="0.25"/>
+    <row r="43" x14ac:dyDescent="0.25"/>
+    <row r="44" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="J1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:Y1"/>
   </mergeCells>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="Z3:AB16" formulaRange="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98F8A35-DD00-4F74-A994-2B1B61BD3853}">
+  <dimension ref="A4:Y4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="1:25" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="29">
+        <v>1</v>
+      </c>
+      <c r="E4" s="29">
+        <v>0</v>
+      </c>
+      <c r="F4" s="29">
+        <v>2</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="28">
+        <v>2</v>
+      </c>
+      <c r="J4" s="28">
+        <v>1</v>
+      </c>
+      <c r="K4" s="28">
+        <v>1</v>
+      </c>
+      <c r="L4" s="28">
+        <v>1</v>
+      </c>
+      <c r="M4" s="28">
+        <v>0</v>
+      </c>
+      <c r="N4" s="28">
+        <v>1</v>
+      </c>
+      <c r="O4" s="28">
+        <v>0</v>
+      </c>
+      <c r="P4" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="28">
+        <v>0</v>
+      </c>
+      <c r="R4" s="28">
+        <v>1</v>
+      </c>
+      <c r="S4" s="28">
+        <v>0</v>
+      </c>
+      <c r="T4" s="28">
+        <v>0</v>
+      </c>
+      <c r="U4" s="28">
+        <v>1</v>
+      </c>
+      <c r="V4" s="28">
+        <v>1</v>
+      </c>
+      <c r="W4" s="28">
+        <v>0</v>
+      </c>
+      <c r="X4" s="28">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F98E057C991C64EA8C44B2688F4F4E8" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="205ac32a36de600e2ab9bca4f1502e82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0278717-252d-455f-9297-341259384352" xmlns:ns3="67fd2e6b-9b4b-488b-ae5d-884371a2c380" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="423e538afa53ae88b73bb7a22e6ab62a" ns2:_="" ns3:_="">
     <xsd:import namespace="b0278717-252d-455f-9297-341259384352"/>
@@ -4794,7 +5523,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
@@ -4805,17 +5534,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E6D151-5FDE-4AAE-92E5-7A931745F48E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32CEAB00-EB88-42CB-8573-B14217434AB6}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89A60870-5FF0-47F8-9D41-DB5EB726C432}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -4833,21 +5561,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86E1DA6F-9828-4C90-B1DD-F6C5DDCFA33D}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="b0278717-252d-455f-9297-341259384352"/>
-    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E6D151-5FDE-4AAE-92E5-7A931745F48E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>